--- a/ANm/Lanyuak_Maize_results.xlsx
+++ b/ANm/Lanyuak_Maize_results.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,32 +417,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>SOC Baseline (t/ha)</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>SOC Project (t/ha)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>SOC Difference (t/ha)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Delta SOC (t/ha)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>ERs (tCO2e/ha)</t>
         </is>
@@ -481,19 +469,19 @@
         <v>2026</v>
       </c>
       <c r="B3" t="n">
-        <v>100.3180319014169</v>
+        <v>105.0911290272596</v>
       </c>
       <c r="C3" t="n">
         <v>113.9409026286368</v>
       </c>
       <c r="D3" t="n">
-        <v>13.62287072721995</v>
+        <v>8.849773601377194</v>
       </c>
       <c r="E3" t="n">
-        <v>13.62432465481733</v>
+        <v>8.851227528974576</v>
       </c>
       <c r="F3" t="n">
-        <v>49.95585706766354</v>
+        <v>32.45450093957344</v>
       </c>
     </row>
     <row r="4">
@@ -501,19 +489,19 @@
         <v>2027</v>
       </c>
       <c r="B4" t="n">
-        <v>92.593856544213</v>
+        <v>100.0796711615978</v>
       </c>
       <c r="C4" t="n">
         <v>113.9409017419045</v>
       </c>
       <c r="D4" t="n">
-        <v>21.34704519769146</v>
+        <v>13.86123058030667</v>
       </c>
       <c r="E4" t="n">
-        <v>7.72417447047151</v>
+        <v>5.011456978929473</v>
       </c>
       <c r="F4" t="n">
-        <v>28.32197305839554</v>
+        <v>18.37534225607473</v>
       </c>
     </row>
     <row r="5">
@@ -521,19 +509,19 @@
         <v>2028</v>
       </c>
       <c r="B5" t="n">
-        <v>87.31345987929318</v>
+        <v>96.66396804167675</v>
       </c>
       <c r="C5" t="n">
         <v>113.9409009003157</v>
       </c>
       <c r="D5" t="n">
-        <v>26.62744102102251</v>
+        <v>17.27693285863893</v>
       </c>
       <c r="E5" t="n">
-        <v>5.280395823331048</v>
+        <v>3.415702278332262</v>
       </c>
       <c r="F5" t="n">
-        <v>19.36145135221384</v>
+        <v>12.52424168721829</v>
       </c>
     </row>
     <row r="6">
@@ -541,19 +529,19 @@
         <v>2029</v>
       </c>
       <c r="B6" t="n">
-        <v>83.35358173893364</v>
+        <v>94.1146002996029</v>
       </c>
       <c r="C6" t="n">
         <v>113.9409001015723</v>
       </c>
       <c r="D6" t="n">
-        <v>30.58731836263867</v>
+        <v>19.82629980196941</v>
       </c>
       <c r="E6" t="n">
-        <v>3.959877341616163</v>
+        <v>2.549366943330483</v>
       </c>
       <c r="F6" t="n">
-        <v>14.5195502525926</v>
+        <v>9.347678792211772</v>
       </c>
     </row>
     <row r="7">
@@ -561,19 +549,19 @@
         <v>2030</v>
       </c>
       <c r="B7" t="n">
-        <v>80.131828803137</v>
+        <v>92.05291088630329</v>
       </c>
       <c r="C7" t="n">
         <v>113.940899343493</v>
       </c>
       <c r="D7" t="n">
-        <v>33.80907054035599</v>
+        <v>21.88798845718969</v>
       </c>
       <c r="E7" t="n">
-        <v>3.22175217771732</v>
+        <v>2.06168865522028</v>
       </c>
       <c r="F7" t="n">
-        <v>11.81309131829684</v>
+        <v>7.559525069141027</v>
       </c>
     </row>
     <row r="8">
@@ -581,19 +569,19 @@
         <v>2031</v>
       </c>
       <c r="B8" t="n">
-        <v>77.34248555121401</v>
+        <v>90.27974215093516</v>
       </c>
       <c r="C8" t="n">
         <v>113.9408986240075</v>
       </c>
       <c r="D8" t="n">
-        <v>36.59841307279351</v>
+        <v>23.66115647307235</v>
       </c>
       <c r="E8" t="n">
-        <v>2.789342532437516</v>
+        <v>1.773168015882661</v>
       </c>
       <c r="F8" t="n">
-        <v>10.22758928560422</v>
+        <v>6.501616058236422</v>
       </c>
     </row>
     <row r="9">
@@ -601,19 +589,19 @@
         <v>2032</v>
       </c>
       <c r="B9" t="n">
-        <v>74.82338601504935</v>
+        <v>88.68912530415784</v>
       </c>
       <c r="C9" t="n">
         <v>113.9408979411511</v>
       </c>
       <c r="D9" t="n">
-        <v>39.11751192610178</v>
+        <v>25.25177263699329</v>
       </c>
       <c r="E9" t="n">
-        <v>2.519098853308279</v>
+        <v>1.590616163920942</v>
       </c>
       <c r="F9" t="n">
-        <v>9.236695795463689</v>
+        <v>5.832259267710119</v>
       </c>
     </row>
     <row r="10">
@@ -621,19 +609,19 @@
         <v>2033</v>
       </c>
       <c r="B10" t="n">
-        <v>72.48747390656678</v>
+        <v>87.22389285041831</v>
       </c>
       <c r="C10" t="n">
         <v>113.940897293059</v>
       </c>
       <c r="D10" t="n">
-        <v>41.45342338649222</v>
+        <v>26.71700444264069</v>
       </c>
       <c r="E10" t="n">
-        <v>2.335911460390435</v>
+        <v>1.465231805647392</v>
       </c>
       <c r="F10" t="n">
-        <v>8.56500868809826</v>
+        <v>5.372516620707103</v>
       </c>
     </row>
     <row r="11">
@@ -641,19 +629,19 @@
         <v>2034</v>
       </c>
       <c r="B11" t="n">
-        <v>70.28720470807002</v>
+        <v>85.85257915477544</v>
       </c>
       <c r="C11" t="n">
         <v>113.9408966779613</v>
       </c>
       <c r="D11" t="n">
-        <v>43.65369196989124</v>
+        <v>28.08831752318582</v>
       </c>
       <c r="E11" t="n">
-        <v>2.200268583399023</v>
+        <v>1.371313080545136</v>
       </c>
       <c r="F11" t="n">
-        <v>8.067651472463083</v>
+        <v>5.028147961998831</v>
       </c>
     </row>
     <row r="12">
@@ -661,19 +649,19 @@
         <v>2035</v>
       </c>
       <c r="B12" t="n">
-        <v>68.19590518711342</v>
+        <v>84.55731721959694</v>
       </c>
       <c r="C12" t="n">
         <v>113.9408960941782</v>
       </c>
       <c r="D12" t="n">
-        <v>45.74499090706479</v>
+        <v>29.38357887458127</v>
       </c>
       <c r="E12" t="n">
-        <v>2.091298937173548</v>
+        <v>1.295261351395453</v>
       </c>
       <c r="F12" t="n">
-        <v>7.668096102969675</v>
+        <v>4.749291621783328</v>
       </c>
     </row>
     <row r="13">
@@ -681,19 +669,19 @@
         <v>2036</v>
       </c>
       <c r="B13" t="n">
-        <v>66.19797435151968</v>
+        <v>83.32747175000624</v>
       </c>
       <c r="C13" t="n">
         <v>113.9408955401156</v>
       </c>
       <c r="D13" t="n">
-        <v>47.7429211885959</v>
+        <v>30.61342379010934</v>
       </c>
       <c r="E13" t="n">
-        <v>1.997930281531112</v>
+        <v>1.229844915528062</v>
       </c>
       <c r="F13" t="n">
-        <v>7.325744365614075</v>
+        <v>4.509431356936228</v>
       </c>
     </row>
     <row r="14">
@@ -701,19 +689,19 @@
         <v>2037</v>
       </c>
       <c r="B14" t="n">
-        <v>64.28371982276842</v>
+        <v>82.15628139978395</v>
       </c>
       <c r="C14" t="n">
         <v>113.9408950142603</v>
       </c>
       <c r="D14" t="n">
-        <v>49.6571751914919</v>
+        <v>31.78461361447637</v>
       </c>
       <c r="E14" t="n">
-        <v>1.914254002896001</v>
+        <v>1.171189824367033</v>
       </c>
       <c r="F14" t="n">
-        <v>7.018931343952005</v>
+        <v>4.294362689345789</v>
       </c>
     </row>
     <row r="15">
@@ -721,19 +709,19 @@
         <v>2038</v>
       </c>
       <c r="B15" t="n">
-        <v>62.44663211162738</v>
+        <v>81.03908460144643</v>
       </c>
       <c r="C15" t="n">
         <v>113.9408945151764</v>
       </c>
       <c r="D15" t="n">
-        <v>51.49426240354899</v>
+        <v>32.90180991372993</v>
       </c>
       <c r="E15" t="n">
-        <v>1.837087212057085</v>
+        <v>1.117196299253564</v>
       </c>
       <c r="F15" t="n">
-        <v>6.735986444209312</v>
+        <v>4.096386430596401</v>
       </c>
     </row>
     <row r="16">
@@ -741,19 +729,19 @@
         <v>2039</v>
       </c>
       <c r="B16" t="n">
-        <v>60.68194338022865</v>
+        <v>79.97238028758923</v>
       </c>
       <c r="C16" t="n">
         <v>113.9408940415008</v>
       </c>
       <c r="D16" t="n">
-        <v>53.25895066127215</v>
+        <v>33.96851375391157</v>
       </c>
       <c r="E16" t="n">
-        <v>1.764688257723165</v>
+        <v>1.066703840181631</v>
       </c>
       <c r="F16" t="n">
-        <v>6.470523611651605</v>
+        <v>3.911247413999315</v>
       </c>
     </row>
     <row r="17">
@@ -761,19 +749,19 @@
         <v>2040</v>
       </c>
       <c r="B17" t="n">
-        <v>58.98586372829006</v>
+        <v>78.95332928137401</v>
       </c>
       <c r="C17" t="n">
         <v>113.9408935919401</v>
       </c>
       <c r="D17" t="n">
-        <v>54.95502986365006</v>
+        <v>34.98756431056611</v>
       </c>
       <c r="E17" t="n">
-        <v>1.696079202377909</v>
+        <v>1.019050556654548</v>
       </c>
       <c r="F17" t="n">
-        <v>6.218957075385667</v>
+        <v>3.736518707733344</v>
       </c>
     </row>
     <row r="18">
@@ -781,19 +769,19 @@
         <v>2041</v>
       </c>
       <c r="B18" t="n">
-        <v>57.35517513261929</v>
+        <v>77.97948847382594</v>
       </c>
       <c r="C18" t="n">
         <v>113.9408931652666</v>
       </c>
       <c r="D18" t="n">
-        <v>56.58571803264731</v>
+        <v>35.96140469144066</v>
       </c>
       <c r="E18" t="n">
-        <v>1.630688168997246</v>
+        <v>0.9738403808745488</v>
       </c>
       <c r="F18" t="n">
-        <v>5.979189952989901</v>
+        <v>3.570748063206679</v>
       </c>
     </row>
     <row r="19">
@@ -801,19 +789,19 @@
         <v>2042</v>
       </c>
       <c r="B19" t="n">
-        <v>55.78701432252263</v>
+        <v>77.04866807290159</v>
       </c>
       <c r="C19" t="n">
         <v>113.940892760315</v>
       </c>
       <c r="D19" t="n">
-        <v>58.15387843779239</v>
+        <v>36.89222468741343</v>
       </c>
       <c r="E19" t="n">
-        <v>1.568160405145086</v>
+        <v>0.9308199959727688</v>
       </c>
       <c r="F19" t="n">
-        <v>5.749921485531982</v>
+        <v>3.413006651900152</v>
       </c>
     </row>
     <row r="20">
@@ -821,19 +809,19 @@
         <v>2043</v>
       </c>
       <c r="B20" t="n">
-        <v>54.2787555526644</v>
+        <v>76.15885398845677</v>
       </c>
       <c r="C20" t="n">
         <v>113.9408923759796</v>
       </c>
       <c r="D20" t="n">
-        <v>59.66213682331519</v>
+        <v>37.78203838752282</v>
       </c>
       <c r="E20" t="n">
-        <v>1.508258385522794</v>
+        <v>0.8898137001093858</v>
       </c>
       <c r="F20" t="n">
-        <v>5.530280746916911</v>
+        <v>3.262650233734414</v>
       </c>
     </row>
     <row r="21">
@@ -841,19 +829,19 @@
         <v>2044</v>
       </c>
       <c r="B21" t="n">
-        <v>52.82794626631246</v>
+        <v>75.30816474760519</v>
       </c>
       <c r="C21" t="n">
         <v>113.9408920112107</v>
       </c>
       <c r="D21" t="n">
-        <v>61.11294574489822</v>
+        <v>38.63272726360549</v>
       </c>
       <c r="E21" t="n">
-        <v>1.450808921583032</v>
+        <v>0.8506888760826712</v>
       </c>
       <c r="F21" t="n">
-        <v>5.319632712471119</v>
+        <v>3.119192545636461</v>
       </c>
     </row>
     <row r="22">
@@ -861,19 +849,19 @@
         <v>2045</v>
       </c>
       <c r="B22" t="n">
-        <v>51.43227082325754</v>
+        <v>74.49482676659144</v>
       </c>
       <c r="C22" t="n">
         <v>113.9408916650122</v>
       </c>
       <c r="D22" t="n">
-        <v>62.50862084175466</v>
+        <v>39.44606489842076</v>
       </c>
       <c r="E22" t="n">
-        <v>1.395675096856444</v>
+        <v>0.8133376348152694</v>
       </c>
       <c r="F22" t="n">
-        <v>5.117475355140293</v>
+        <v>2.982237994322654</v>
       </c>
     </row>
     <row r="23">
@@ -881,19 +869,19 @@
         <v>2046</v>
       </c>
       <c r="B23" t="n">
-        <v>50.08952917577319</v>
+        <v>73.71715942788097</v>
       </c>
       <c r="C23" t="n">
         <v>113.9408913364387</v>
       </c>
       <c r="D23" t="n">
-        <v>63.85136216066551</v>
+        <v>40.22373190855772</v>
       </c>
       <c r="E23" t="n">
-        <v>1.342741318910846</v>
+        <v>0.777667010136966</v>
       </c>
       <c r="F23" t="n">
-        <v>4.923384836006437</v>
+        <v>2.851445703835542</v>
       </c>
     </row>
     <row r="24">
@@ -901,19 +889,19 @@
         <v>2047</v>
       </c>
       <c r="B24" t="n">
-        <v>48.79762355825806</v>
+        <v>72.97356543811884</v>
       </c>
       <c r="C24" t="n">
         <v>113.9408910245929</v>
       </c>
       <c r="D24" t="n">
-        <v>65.14326746633483</v>
+        <v>40.96732558647405</v>
       </c>
       <c r="E24" t="n">
-        <v>1.291905305669324</v>
+        <v>0.7435936779163228</v>
       </c>
       <c r="F24" t="n">
-        <v>4.736986120787523</v>
+        <v>2.72651015235985</v>
       </c>
     </row>
     <row r="25">
@@ -921,19 +909,19 @@
         <v>2048</v>
       </c>
       <c r="B25" t="n">
-        <v>47.55454952101586</v>
+        <v>72.26252407042759</v>
       </c>
       <c r="C25" t="n">
         <v>113.9408907286231</v>
       </c>
       <c r="D25" t="n">
-        <v>66.38634120760729</v>
+        <v>41.67836665819556</v>
       </c>
       <c r="E25" t="n">
-        <v>1.243073741272454</v>
+        <v>0.7110410717215103</v>
       </c>
       <c r="F25" t="n">
-        <v>4.557937051332331</v>
+        <v>2.607150596312204</v>
       </c>
     </row>
     <row r="26">
@@ -941,19 +929,19 @@
         <v>2049</v>
       </c>
       <c r="B26" t="n">
-        <v>46.35838936314073</v>
+        <v>71.58258601910215</v>
       </c>
       <c r="C26" t="n">
         <v>113.9408904477213</v>
       </c>
       <c r="D26" t="n">
-        <v>67.58250108458058</v>
+        <v>42.35830442861916</v>
       </c>
       <c r="E26" t="n">
-        <v>1.196159876973297</v>
+        <v>0.6799377704236065</v>
       </c>
       <c r="F26" t="n">
-        <v>4.38591954890209</v>
+        <v>2.49310515821989</v>
       </c>
     </row>
     <row r="27">
@@ -961,19 +949,19 @@
         <v>2050</v>
       </c>
       <c r="B27" t="n">
-        <v>45.20730693066831</v>
+        <v>70.93236918932784</v>
       </c>
       <c r="C27" t="n">
         <v>113.9408901811202</v>
       </c>
       <c r="D27" t="n">
-        <v>68.73358325045186</v>
+        <v>43.00852099179232</v>
       </c>
       <c r="E27" t="n">
-        <v>1.151082165871273</v>
+        <v>0.65021656317316</v>
       </c>
       <c r="F27" t="n">
-        <v>4.220634608194668</v>
+        <v>2.384127398301587</v>
       </c>
     </row>
     <row r="28">
@@ -981,19 +969,19 @@
         <v>2051</v>
       </c>
       <c r="B28" t="n">
-        <v>44.09954322783643</v>
+        <v>70.31055505906187</v>
       </c>
       <c r="C28" t="n">
         <v>113.9408899280917</v>
       </c>
       <c r="D28" t="n">
-        <v>69.84134670025531</v>
+        <v>43.63033486902987</v>
       </c>
       <c r="E28" t="n">
-        <v>1.107763449803457</v>
+        <v>0.6218138772375426</v>
       </c>
       <c r="F28" t="n">
-        <v>4.061799315946009</v>
+        <v>2.279984216537656</v>
       </c>
     </row>
     <row r="29">
@@ -1001,19 +989,19 @@
         <v>2052</v>
       </c>
       <c r="B29" t="n">
-        <v>43.03341254413452</v>
+        <v>69.71588541674161</v>
       </c>
       <c r="C29" t="n">
         <v>113.9408896879449</v>
       </c>
       <c r="D29" t="n">
-        <v>70.90747714381042</v>
+        <v>44.22500427120333</v>
       </c>
       <c r="E29" t="n">
-        <v>1.06613044355511</v>
+        <v>0.5946694021734658</v>
       </c>
       <c r="F29" t="n">
-        <v>3.909144959702071</v>
+        <v>2.180454474636041</v>
       </c>
     </row>
     <row r="30">
@@ -1021,19 +1009,19 @@
         <v>2053</v>
       </c>
       <c r="B30" t="n">
-        <v>42.00729893481606</v>
+        <v>69.14715936678485</v>
       </c>
       <c r="C30" t="n">
         <v>113.9408894600241</v>
       </c>
       <c r="D30" t="n">
-        <v>71.93359052520805</v>
+        <v>44.79373009323925</v>
       </c>
       <c r="E30" t="n">
-        <v>1.026113381397622</v>
+        <v>0.5687258220359155</v>
       </c>
       <c r="F30" t="n">
-        <v>3.762415731791279</v>
+        <v>2.08532801413169</v>
       </c>
     </row>
     <row r="31">
@@ -1041,19 +1029,19 @@
         <v>2054</v>
       </c>
       <c r="B31" t="n">
-        <v>41.0196529642245</v>
+        <v>68.60323054179347</v>
       </c>
       <c r="C31" t="n">
         <v>113.9408892437067</v>
       </c>
       <c r="D31" t="n">
-        <v>72.92123627948217</v>
+        <v>45.3376587019132</v>
       </c>
       <c r="E31" t="n">
-        <v>0.9876457542741264</v>
+        <v>0.5439286086739514</v>
       </c>
       <c r="F31" t="n">
-        <v>3.621367765671797</v>
+        <v>1.994404898471155</v>
       </c>
     </row>
     <row r="32">
@@ -1061,19 +1049,19 @@
         <v>2055</v>
       </c>
       <c r="B32" t="n">
-        <v>40.06898865948371</v>
+        <v>68.0830044854449</v>
       </c>
       <c r="C32" t="n">
         <v>113.9408890384019</v>
       </c>
       <c r="D32" t="n">
-        <v>73.87190037891821</v>
+        <v>45.85788455295702</v>
       </c>
       <c r="E32" t="n">
-        <v>0.9506640994360396</v>
+        <v>0.5202258510438185</v>
       </c>
       <c r="F32" t="n">
-        <v>3.485768364598812</v>
+        <v>1.907494787160668</v>
       </c>
     </row>
     <row r="33">
@@ -1081,19 +1069,19 @@
         <v>2056</v>
       </c>
       <c r="B33" t="n">
-        <v>39.15388064259839</v>
+        <v>67.58543618354948</v>
       </c>
       <c r="C33" t="n">
         <v>113.9408888435493</v>
       </c>
       <c r="D33" t="n">
-        <v>74.78700820095091</v>
+        <v>46.35545265999981</v>
       </c>
       <c r="E33" t="n">
-        <v>0.9151078220326951</v>
+        <v>0.4975681070427953</v>
       </c>
       <c r="F33" t="n">
-        <v>3.355395347453216</v>
+        <v>1.824416392490249</v>
       </c>
     </row>
     <row r="34">
@@ -1101,19 +1089,19 @@
         <v>2057</v>
       </c>
       <c r="B34" t="n">
-        <v>38.27296142012685</v>
+        <v>67.1095277281094</v>
       </c>
       <c r="C34" t="n">
         <v>113.9408886586166</v>
       </c>
       <c r="D34" t="n">
-        <v>75.6679272384898</v>
+        <v>46.83136093050724</v>
       </c>
       <c r="E34" t="n">
-        <v>0.880919037538888</v>
+        <v>0.475908270507432</v>
       </c>
       <c r="F34" t="n">
-        <v>3.230036470975923</v>
+        <v>1.744996991860584</v>
       </c>
     </row>
     <row r="35">
@@ -1121,19 +1109,19 @@
         <v>2058</v>
       </c>
       <c r="B35" t="n">
-        <v>37.42491881572935</v>
+        <v>66.6543261033114</v>
       </c>
       <c r="C35" t="n">
         <v>113.9408884830989</v>
       </c>
       <c r="D35" t="n">
-        <v>76.51596966736957</v>
+        <v>47.28656237978753</v>
       </c>
       <c r="E35" t="n">
-        <v>0.8480424288797792</v>
+        <v>0.4552014492802812</v>
       </c>
       <c r="F35" t="n">
-        <v>3.109488905892524</v>
+        <v>1.669071980694364</v>
       </c>
     </row>
     <row r="36">
@@ -1141,19 +1129,19 @@
         <v>2059</v>
       </c>
       <c r="B36" t="n">
-        <v>36.60849353438679</v>
+        <v>66.21892108474499</v>
       </c>
       <c r="C36" t="n">
         <v>113.9408883165168</v>
       </c>
       <c r="D36" t="n">
-        <v>77.33239478213005</v>
+        <v>47.72196723177184</v>
       </c>
       <c r="E36" t="n">
-        <v>0.8164251147604773</v>
+        <v>0.4354048519843161</v>
       </c>
       <c r="F36" t="n">
-        <v>2.99355875412175</v>
+        <v>1.596484457275826</v>
       </c>
     </row>
     <row r="37">
@@ -1161,19 +1149,19 @@
         <v>2060</v>
       </c>
       <c r="B37" t="n">
-        <v>35.8224768491587</v>
+        <v>65.80244324456469</v>
       </c>
       <c r="C37" t="n">
         <v>113.9408881584154</v>
       </c>
       <c r="D37" t="n">
-        <v>78.11841130925667</v>
+        <v>48.13844491385069</v>
       </c>
       <c r="E37" t="n">
-        <v>0.7860165271266197</v>
+        <v>0.4164776820788489</v>
       </c>
       <c r="F37" t="n">
-        <v>2.882060599464273</v>
+        <v>1.527084834289113</v>
       </c>
     </row>
     <row r="38">
@@ -1181,19 +1169,19 @@
         <v>2061</v>
       </c>
       <c r="B38" t="n">
-        <v>35.06570840265632</v>
+        <v>65.40406205623503</v>
       </c>
       <c r="C38" t="n">
         <v>113.9408880083629</v>
       </c>
       <c r="D38" t="n">
-        <v>78.87517960570659</v>
+        <v>48.53682595212787</v>
       </c>
       <c r="E38" t="n">
-        <v>0.7567682964499198</v>
+        <v>0.3983810382771793</v>
       </c>
       <c r="F38" t="n">
-        <v>2.77481708698304</v>
+        <v>1.460730473682991</v>
       </c>
     </row>
     <row r="39">
@@ -1201,19 +1189,19 @@
         <v>2062</v>
       </c>
       <c r="B39" t="n">
-        <v>34.33707411629353</v>
+        <v>65.02298409313971</v>
       </c>
       <c r="C39" t="n">
         <v>113.9408878659496</v>
       </c>
       <c r="D39" t="n">
-        <v>79.6038137496561</v>
+        <v>48.91790377280992</v>
       </c>
       <c r="E39" t="n">
-        <v>0.7286341439495061</v>
+        <v>0.3810778206820515</v>
       </c>
       <c r="F39" t="n">
-        <v>2.671658527814856</v>
+        <v>1.397285342500856</v>
       </c>
     </row>
     <row r="40">
@@ -1221,19 +1209,19 @@
         <v>2063</v>
       </c>
       <c r="B40" t="n">
-        <v>33.63550420102801</v>
+        <v>64.6584513158182</v>
       </c>
       <c r="C40" t="n">
         <v>113.9408877307867</v>
       </c>
       <c r="D40" t="n">
-        <v>80.30538352975864</v>
+        <v>49.28243641496846</v>
       </c>
       <c r="E40" t="n">
-        <v>0.7015697801025453</v>
+        <v>0.3645326421585366</v>
       </c>
       <c r="F40" t="n">
-        <v>2.572422527042666</v>
+        <v>1.336619687914634</v>
       </c>
     </row>
     <row r="41">
@@ -1241,19 +1229,19 @@
         <v>2064</v>
       </c>
       <c r="B41" t="n">
-        <v>32.95997126381691</v>
+        <v>64.3097394429838</v>
       </c>
       <c r="C41" t="n">
         <v>113.9408876025048</v>
       </c>
       <c r="D41" t="n">
-        <v>80.9809163386879</v>
+        <v>49.63114815952102</v>
       </c>
       <c r="E41" t="n">
-        <v>0.6755328089292618</v>
+        <v>0.3487117445525598</v>
       </c>
       <c r="F41" t="n">
-        <v>2.476953632740627</v>
+        <v>1.278609730026053</v>
       </c>
     </row>
     <row r="42">
@@ -1261,19 +1249,19 @@
         <v>2065</v>
       </c>
       <c r="B42" t="n">
-        <v>32.30948850443712</v>
+        <v>63.97615640180651</v>
       </c>
       <c r="C42" t="n">
         <v>113.9408874807538</v>
       </c>
       <c r="D42" t="n">
-        <v>81.63139897631666</v>
+        <v>49.96473107894728</v>
       </c>
       <c r="E42" t="n">
-        <v>0.6504826376287554</v>
+        <v>0.3335829194262629</v>
       </c>
       <c r="F42" t="n">
-        <v>2.38510300463877</v>
+        <v>1.223137371229631</v>
       </c>
     </row>
   </sheetData>
